--- a/TABLEAU_DE_SYNTHESE.xlsx
+++ b/TABLEAU_DE_SYNTHESE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29930"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\BTS\2026\CIRCULAIRES NATIONALES\SIO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\portfolio-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A90414C-1A79-4688-91F3-86F5BEA2845A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C972D0F9-6747-48C9-B9C0-714A7181EAA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-118" yWindow="-118" windowWidth="25370" windowHeight="15330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="51">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -255,7 +254,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -335,6 +334,19 @@
       <sz val="14"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <sz val="28"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="28"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -735,7 +747,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -800,15 +812,45 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -818,6 +860,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -839,37 +884,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1181,16 +1199,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AQ80"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.875" defaultRowHeight="12.45" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="70.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" style="1" customWidth="1"/>
-    <col min="3" max="8" width="18.7109375" style="1" customWidth="1"/>
-    <col min="9" max="43" width="11.42578125" customWidth="1"/>
-    <col min="44" max="16384" width="10.85546875" style="1"/>
+    <col min="1" max="1" width="70.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.875" style="1" customWidth="1"/>
+    <col min="3" max="8" width="18.75" style="1" customWidth="1"/>
+    <col min="9" max="43" width="11.375" customWidth="1"/>
+    <col min="44" max="16384" width="10.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1">
+    <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
@@ -1204,7 +1222,7 @@
       </c>
       <c r="H1" s="24"/>
     </row>
-    <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1">
+    <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>2</v>
       </c>
@@ -1216,31 +1234,31 @@
       <c r="G2" s="24"/>
       <c r="H2" s="24"/>
     </row>
-    <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1">
-      <c r="A3" s="35" t="s">
+    <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="41" t="s">
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="36"/>
-      <c r="H3" s="42"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="32"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1">
-      <c r="A4" s="38" t="s">
+    <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="40"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="30"/>
       <c r="F4" s="12" t="s">
         <v>6</v>
       </c>
@@ -1251,23 +1269,23 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1">
-      <c r="A5" s="32" t="s">
+    <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="33"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="34"/>
-    </row>
-    <row r="6" spans="1:43" ht="90" customHeight="1">
-      <c r="A6" s="22" t="s">
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="45"/>
+    </row>
+    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="41" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1289,9 +1307,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1">
-      <c r="A7" s="23"/>
-      <c r="B7" s="31"/>
+    <row r="7" spans="1:43" s="2" customFormat="1" ht="325" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="34"/>
+      <c r="B7" s="42"/>
       <c r="C7" s="20" t="s">
         <v>18</v>
       </c>
@@ -1346,17 +1364,17 @@
       <c r="AP7"/>
       <c r="AQ7"/>
     </row>
-    <row r="8" spans="1:43" s="2" customFormat="1" ht="18">
-      <c r="A8" s="25" t="s">
+    <row r="8" spans="1:43" s="2" customFormat="1" ht="17.7" x14ac:dyDescent="0.2">
+      <c r="A8" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="27"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="37"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1393,7 +1411,7 @@
       <c r="AP8"/>
       <c r="AQ8"/>
     </row>
-    <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
         <v>25</v>
       </c>
@@ -1407,7 +1425,7 @@
       </c>
       <c r="F9" s="14"/>
       <c r="G9" s="14"/>
-      <c r="H9" s="44" t="s">
+      <c r="H9" s="23" t="s">
         <v>27</v>
       </c>
       <c r="I9"/>
@@ -1446,7 +1464,7 @@
       <c r="AP9"/>
       <c r="AQ9"/>
     </row>
-    <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
         <v>28</v>
       </c>
@@ -1458,7 +1476,7 @@
       <c r="E10" s="14"/>
       <c r="F10" s="14"/>
       <c r="G10" s="14"/>
-      <c r="H10" s="44" t="s">
+      <c r="H10" s="23" t="s">
         <v>27</v>
       </c>
       <c r="I10"/>
@@ -1497,7 +1515,7 @@
       <c r="AP10"/>
       <c r="AQ10"/>
     </row>
-    <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
         <v>30</v>
       </c>
@@ -1548,7 +1566,7 @@
       <c r="AP11"/>
       <c r="AQ11"/>
     </row>
-    <row r="12" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="12" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
         <v>32</v>
       </c>
@@ -1599,7 +1617,7 @@
       <c r="AP12"/>
       <c r="AQ12"/>
     </row>
-    <row r="13" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="13" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
         <v>34</v>
       </c>
@@ -1650,11 +1668,11 @@
       <c r="AP13"/>
       <c r="AQ13"/>
     </row>
-    <row r="14" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="14" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="22" t="s">
         <v>37</v>
       </c>
       <c r="C14" s="14"/>
@@ -1701,7 +1719,7 @@
       <c r="AP14"/>
       <c r="AQ14"/>
     </row>
-    <row r="15" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="15" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
         <v>38</v>
       </c>
@@ -1752,7 +1770,7 @@
       <c r="AP15"/>
       <c r="AQ15"/>
     </row>
-    <row r="16" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="16" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
         <v>40</v>
       </c>
@@ -1805,7 +1823,7 @@
       <c r="AP16"/>
       <c r="AQ16"/>
     </row>
-    <row r="17" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="17" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
         <v>42</v>
       </c>
@@ -1856,7 +1874,7 @@
       <c r="AP17"/>
       <c r="AQ17"/>
     </row>
-    <row r="18" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="18" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9"/>
       <c r="B18" s="8"/>
       <c r="C18" s="14"/>
@@ -1901,17 +1919,17 @@
       <c r="AP18"/>
       <c r="AQ18"/>
     </row>
-    <row r="19" spans="1:43" s="2" customFormat="1" ht="18">
-      <c r="A19" s="45" t="s">
+    <row r="19" spans="1:43" s="2" customFormat="1" ht="17.7" x14ac:dyDescent="0.2">
+      <c r="A19" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="29"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="40"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1948,7 +1966,7 @@
       <c r="AP19"/>
       <c r="AQ19"/>
     </row>
-    <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
         <v>45</v>
       </c>
@@ -1958,7 +1976,9 @@
       <c r="C20" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="14"/>
+      <c r="D20" s="47" t="s">
+        <v>27</v>
+      </c>
       <c r="E20" s="14"/>
       <c r="F20" s="14"/>
       <c r="G20" s="14"/>
@@ -1999,7 +2019,7 @@
       <c r="AP20"/>
       <c r="AQ20"/>
     </row>
-    <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
         <v>47</v>
       </c>
@@ -2009,7 +2029,9 @@
       <c r="C21" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D21" s="14"/>
+      <c r="D21" s="47" t="s">
+        <v>27</v>
+      </c>
       <c r="E21" s="14"/>
       <c r="F21" s="14"/>
       <c r="G21" s="14"/>
@@ -2050,7 +2072,7 @@
       <c r="AP21"/>
       <c r="AQ21"/>
     </row>
-    <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
         <v>48</v>
       </c>
@@ -2060,7 +2082,7 @@
       <c r="C22" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="46" t="s">
         <v>27</v>
       </c>
       <c r="E22" s="14"/>
@@ -2103,7 +2125,7 @@
       <c r="AP22"/>
       <c r="AQ22"/>
     </row>
-    <row r="23" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="23" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
         <v>49</v>
       </c>
@@ -2113,7 +2135,9 @@
       <c r="C23" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D23" s="14"/>
+      <c r="D23" s="47" t="s">
+        <v>27</v>
+      </c>
       <c r="E23" s="14"/>
       <c r="F23" s="14"/>
       <c r="G23" s="19" t="s">
@@ -2156,7 +2180,7 @@
       <c r="AP23"/>
       <c r="AQ23"/>
     </row>
-    <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9"/>
       <c r="B24" s="8"/>
       <c r="C24" s="14"/>
@@ -2201,7 +2225,7 @@
       <c r="AP24"/>
       <c r="AQ24"/>
     </row>
-    <row r="25" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="25" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9"/>
       <c r="B25" s="8"/>
       <c r="C25" s="14"/>
@@ -2246,17 +2270,17 @@
       <c r="AP25"/>
       <c r="AQ25"/>
     </row>
-    <row r="26" spans="1:43" s="2" customFormat="1" ht="18">
-      <c r="A26" s="45" t="s">
+    <row r="26" spans="1:43" s="2" customFormat="1" ht="17.7" x14ac:dyDescent="0.2">
+      <c r="A26" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="29"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="40"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2293,7 +2317,7 @@
       <c r="AP26"/>
       <c r="AQ26"/>
     </row>
-    <row r="27" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="27" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="9"/>
       <c r="B27" s="8"/>
       <c r="C27" s="14"/>
@@ -2338,7 +2362,7 @@
       <c r="AP27"/>
       <c r="AQ27"/>
     </row>
-    <row r="28" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="28" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9"/>
       <c r="B28" s="8"/>
       <c r="C28" s="14"/>
@@ -2383,7 +2407,7 @@
       <c r="AP28"/>
       <c r="AQ28"/>
     </row>
-    <row r="29" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="29" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="9"/>
       <c r="B29" s="8"/>
       <c r="C29" s="14"/>
@@ -2428,7 +2452,7 @@
       <c r="AP29"/>
       <c r="AQ29"/>
     </row>
-    <row r="30" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="30" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9"/>
       <c r="B30" s="8"/>
       <c r="C30" s="14"/>
@@ -2473,7 +2497,7 @@
       <c r="AP30"/>
       <c r="AQ30"/>
     </row>
-    <row r="31" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="31" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9"/>
       <c r="B31" s="8"/>
       <c r="C31" s="14"/>
@@ -2518,7 +2542,7 @@
       <c r="AP31"/>
       <c r="AQ31"/>
     </row>
-    <row r="32" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="32" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9"/>
       <c r="B32" s="8"/>
       <c r="C32" s="14"/>
@@ -2563,7 +2587,7 @@
       <c r="AP32"/>
       <c r="AQ32"/>
     </row>
-    <row r="33" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1">
+    <row r="33" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10"/>
       <c r="B33" s="11"/>
       <c r="C33" s="16"/>
@@ -2608,7 +2632,7 @@
       <c r="AP33"/>
       <c r="AQ33"/>
     </row>
-    <row r="34" spans="1:43" s="2" customFormat="1" ht="15">
+    <row r="34" spans="1:43" s="2" customFormat="1" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A34" s="5"/>
       <c r="B34" s="3"/>
       <c r="C34" s="4"/>
@@ -2653,59 +2677,54 @@
       <c r="AP34"/>
       <c r="AQ34"/>
     </row>
-    <row r="35" spans="1:43" customFormat="1"/>
-    <row r="36" spans="1:43" customFormat="1"/>
-    <row r="37" spans="1:43" customFormat="1"/>
-    <row r="38" spans="1:43" customFormat="1"/>
-    <row r="39" spans="1:43" customFormat="1"/>
-    <row r="40" spans="1:43" customFormat="1"/>
-    <row r="41" spans="1:43" customFormat="1"/>
-    <row r="42" spans="1:43" customFormat="1"/>
-    <row r="43" spans="1:43" customFormat="1"/>
-    <row r="44" spans="1:43" customFormat="1"/>
-    <row r="45" spans="1:43" customFormat="1"/>
-    <row r="46" spans="1:43" customFormat="1"/>
-    <row r="47" spans="1:43" customFormat="1"/>
-    <row r="48" spans="1:43" customFormat="1"/>
-    <row r="49" customFormat="1"/>
-    <row r="50" customFormat="1"/>
-    <row r="51" customFormat="1"/>
-    <row r="52" customFormat="1"/>
-    <row r="53" customFormat="1"/>
-    <row r="54" customFormat="1"/>
-    <row r="55" customFormat="1"/>
-    <row r="56" customFormat="1"/>
-    <row r="57" customFormat="1"/>
-    <row r="58" customFormat="1"/>
-    <row r="59" customFormat="1"/>
-    <row r="60" customFormat="1"/>
-    <row r="61" customFormat="1"/>
-    <row r="62" customFormat="1"/>
-    <row r="63" customFormat="1"/>
-    <row r="64" customFormat="1"/>
-    <row r="65" customFormat="1"/>
-    <row r="66" customFormat="1"/>
-    <row r="67" customFormat="1"/>
-    <row r="68" customFormat="1"/>
-    <row r="69" customFormat="1"/>
-    <row r="70" customFormat="1"/>
-    <row r="71" customFormat="1"/>
-    <row r="72" customFormat="1"/>
-    <row r="73" customFormat="1"/>
-    <row r="74" customFormat="1"/>
-    <row r="75" customFormat="1"/>
-    <row r="76" customFormat="1"/>
-    <row r="77" customFormat="1"/>
-    <row r="78" customFormat="1"/>
-    <row r="79" customFormat="1"/>
-    <row r="80" customFormat="1"/>
+    <row r="35" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="36" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="37" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="39" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="40" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="41" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="42" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="44" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="45" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="49" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="50" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="51" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="52" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="54" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="55" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="56" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="57" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="58" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="59" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="60" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="61" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="62" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="63" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="64" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="65" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="66" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="68" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="69" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="70" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="71" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="72" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="73" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="74" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="75" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="76" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="77" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="78" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="79" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="80" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2713,11 +2732,16 @@
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="48" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="48" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
--- a/TABLEAU_DE_SYNTHESE.xlsx
+++ b/TABLEAU_DE_SYNTHESE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\portfolio-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\portfolio-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C972D0F9-6747-48C9-B9C0-714A7181EAA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D47A15-009B-41F8-8CC3-B0C79619ED89}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-118" yWindow="-118" windowWidth="25370" windowHeight="15330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21810" windowHeight="10590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
@@ -23,22 +23,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="56">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -175,9 +165,6 @@
     <t>Création et déploiement d'un serveur APACHE web Debian 11</t>
   </si>
   <si>
-    <t>10/01/2026 au 16/01/2026</t>
-  </si>
-  <si>
     <t>Gestion et réparation d'un RAID5 sur une machine Windows server 2022.</t>
   </si>
   <si>
@@ -185,9 +172,6 @@
   </si>
   <si>
     <t>Installation et configuration de OpenMediaVault sur une machine Linux Debian 12 pour en faire un NAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/03/2026 au 27/03/2026 </t>
   </si>
   <si>
     <r>
@@ -245,6 +229,27 @@
       </rPr>
       <t>Ville de Paris</t>
     </r>
+  </si>
+  <si>
+    <t>Mise en supervision de climatiseurs INROW sur Centreon</t>
+  </si>
+  <si>
+    <t>Mis à jour de l’application Centreon elle-même</t>
+  </si>
+  <si>
+    <t>Importation en supervision dans Centreon d’une liste d’hôtes écrit sous format CSV (automatisé via un script BASH.)</t>
+  </si>
+  <si>
+    <t>Mise en place et déploiement d’un poste de travail préconfiguré pour qu’il soit opérationnel.</t>
+  </si>
+  <si>
+    <t>01/09/2026 à aujourd'hui</t>
+  </si>
+  <si>
+    <t>10/01/2026 au 18/01/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/02/2026 au 06/03/2026 </t>
   </si>
 </sst>
 </file>
@@ -747,7 +752,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -818,9 +823,57 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -844,51 +897,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -909,9 +917,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -949,9 +957,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -984,9 +992,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1019,9 +1044,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1199,66 +1241,66 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AQ80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.875" defaultRowHeight="12.45" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="70.375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.875" style="1" customWidth="1"/>
-    <col min="3" max="8" width="18.75" style="1" customWidth="1"/>
-    <col min="9" max="43" width="11.375" customWidth="1"/>
-    <col min="44" max="16384" width="10.875" style="1"/>
+    <col min="1" max="1" width="70.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" style="1" customWidth="1"/>
+    <col min="3" max="8" width="18.7109375" style="1" customWidth="1"/>
+    <col min="9" max="43" width="11.42578125" customWidth="1"/>
+    <col min="44" max="16384" width="10.85546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="24"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="31" t="s">
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="26"/>
-      <c r="H3" s="32"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="48"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="30"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="46"/>
       <c r="F4" s="12" t="s">
         <v>6</v>
       </c>
@@ -1270,22 +1312,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="45"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="36" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1307,9 +1349,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:43" s="2" customFormat="1" ht="325" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="34"/>
-      <c r="B7" s="42"/>
+    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="28"/>
+      <c r="B7" s="37"/>
       <c r="C7" s="20" t="s">
         <v>18</v>
       </c>
@@ -1364,17 +1406,17 @@
       <c r="AP7"/>
       <c r="AQ7"/>
     </row>
-    <row r="8" spans="1:43" s="2" customFormat="1" ht="17.7" x14ac:dyDescent="0.2">
-      <c r="A8" s="35" t="s">
+    <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+      <c r="A8" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="36"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="37"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="32"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1724,7 +1766,7 @@
         <v>38</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
@@ -1772,10 +1814,10 @@
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>40</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>41</v>
       </c>
       <c r="C16" s="19" t="s">
         <v>27</v>
@@ -1825,10 +1867,10 @@
     </row>
     <row r="17" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
@@ -1919,17 +1961,17 @@
       <c r="AP18"/>
       <c r="AQ18"/>
     </row>
-    <row r="19" spans="1:43" s="2" customFormat="1" ht="17.7" x14ac:dyDescent="0.2">
-      <c r="A19" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" s="39"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="40"/>
+    <row r="19" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+      <c r="A19" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="35"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1968,15 +2010,15 @@
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C20" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="47" t="s">
+      <c r="D20" s="25" t="s">
         <v>27</v>
       </c>
       <c r="E20" s="14"/>
@@ -2021,15 +2063,15 @@
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C21" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D21" s="47" t="s">
+      <c r="D21" s="25" t="s">
         <v>27</v>
       </c>
       <c r="E21" s="14"/>
@@ -2074,15 +2116,15 @@
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C22" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D22" s="46" t="s">
+      <c r="D22" s="24" t="s">
         <v>27</v>
       </c>
       <c r="E22" s="14"/>
@@ -2127,20 +2169,20 @@
     </row>
     <row r="23" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C23" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D23" s="47" t="s">
+      <c r="D23" s="25" t="s">
         <v>27</v>
       </c>
       <c r="E23" s="14"/>
       <c r="F23" s="14"/>
-      <c r="G23" s="19" t="s">
+      <c r="G23" s="24" t="s">
         <v>27</v>
       </c>
       <c r="H23" s="15"/>
@@ -2270,17 +2312,17 @@
       <c r="AP25"/>
       <c r="AQ25"/>
     </row>
-    <row r="26" spans="1:43" s="2" customFormat="1" ht="17.7" x14ac:dyDescent="0.2">
-      <c r="A26" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" s="39"/>
-      <c r="C26" s="39"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="39"/>
-      <c r="H26" s="40"/>
+    <row r="26" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+      <c r="A26" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="34"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="35"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2318,14 +2360,24 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="9"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="14"/>
+      <c r="A27" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>27</v>
+      </c>
       <c r="D27" s="14"/>
       <c r="E27" s="14"/>
       <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="15"/>
+      <c r="G27" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H27" s="26" t="s">
+        <v>27</v>
+      </c>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2363,13 +2415,23 @@
       <c r="AQ27"/>
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="9"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
+      <c r="A28" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>27</v>
+      </c>
       <c r="E28" s="14"/>
       <c r="F28" s="14"/>
-      <c r="G28" s="19"/>
+      <c r="G28" s="24" t="s">
+        <v>27</v>
+      </c>
       <c r="H28" s="15"/>
       <c r="I28"/>
       <c r="J28"/>
@@ -2408,14 +2470,26 @@
       <c r="AQ28"/>
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="9"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
+      <c r="A29" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>27</v>
+      </c>
       <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
+      <c r="F29" s="25" t="s">
+        <v>27</v>
+      </c>
       <c r="G29" s="14"/>
-      <c r="H29" s="15"/>
+      <c r="H29" s="26" t="s">
+        <v>27</v>
+      </c>
       <c r="I29"/>
       <c r="J29"/>
       <c r="K29"/>
@@ -2453,13 +2527,21 @@
       <c r="AQ29"/>
     </row>
     <row r="30" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="9"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="14"/>
+      <c r="A30" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" s="25" t="s">
+        <v>27</v>
+      </c>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
       <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
+      <c r="G30" s="25" t="s">
+        <v>27</v>
+      </c>
       <c r="H30" s="15"/>
       <c r="I30"/>
       <c r="J30"/>
@@ -2632,7 +2714,7 @@
       <c r="AP33"/>
       <c r="AQ33"/>
     </row>
-    <row r="34" spans="1:43" s="2" customFormat="1" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:43" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A34" s="5"/>
       <c r="B34" s="3"/>
       <c r="C34" s="4"/>
@@ -2725,6 +2807,11 @@
     <row r="80" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2732,11 +2819,6 @@
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/TABLEAU_DE_SYNTHESE.xlsx
+++ b/TABLEAU_DE_SYNTHESE.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\portfolio-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D47A15-009B-41F8-8CC3-B0C79619ED89}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFAAD410-D816-4EE7-B33B-A23AB022145C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21810" windowHeight="10590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$32</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="52">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -123,37 +123,13 @@
     <t>Réalisation en cours de formation : Campus Montsouris</t>
   </si>
   <si>
-    <t>Conception et structuration de mon Portfolio professionel numérique</t>
-  </si>
-  <si>
-    <t>02/10/2025 à aujourd'hui</t>
-  </si>
-  <si>
     <t>X</t>
   </si>
   <si>
-    <t>Optimisation et mise à niveau de mon compte linkedin professionel</t>
-  </si>
-  <si>
-    <t>07/09/2025 à aujourd'hui</t>
-  </si>
-  <si>
-    <t>Mise en place d'un dispositif de veille</t>
-  </si>
-  <si>
-    <t>08/01/2026 à aujourd'hui</t>
-  </si>
-  <si>
     <t>Création et configuration de machines virtuelles sur VirtualBox</t>
   </si>
   <si>
     <t>19/09/2025 au 19/09/2025</t>
-  </si>
-  <si>
-    <t>Sertissage d'une prise de câble RJ45</t>
-  </si>
-  <si>
-    <t>28/11/2025 au 28/11/2025</t>
   </si>
   <si>
     <t>Mise en place d'un agent de récupération EFS sur une machine windows server 2022.</t>
@@ -250,6 +226,18 @@
   </si>
   <si>
     <t xml:space="preserve">27/02/2026 au 06/03/2026 </t>
+  </si>
+  <si>
+    <t>Simuler et tester des réseaux informatiques avec Filius</t>
+  </si>
+  <si>
+    <t>Interconnexion de deux réseaux locaux virtuels via routage statique sous VirtualBox</t>
+  </si>
+  <si>
+    <t>13/06/2026 au 13/06/2026</t>
+  </si>
+  <si>
+    <t>20/03/2026 au 27/03/2026</t>
   </si>
 </sst>
 </file>
@@ -752,7 +740,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -819,9 +807,6 @@
     </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1240,7 +1225,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AQ80"/>
+  <dimension ref="A1:AQ78"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="70.42578125" style="1" customWidth="1"/>
@@ -1251,56 +1236,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="29"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="47" t="s">
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="42"/>
-      <c r="H3" s="48"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="47"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="46"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
       <c r="F4" s="12" t="s">
         <v>6</v>
       </c>
@@ -1312,22 +1297,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="40"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="39"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="35" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1350,8 +1335,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
-      <c r="B7" s="37"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="36"/>
       <c r="C7" s="20" t="s">
         <v>18</v>
       </c>
@@ -1407,16 +1392,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="32"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="31"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1455,21 +1440,19 @@
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="19"/>
+        <v>27</v>
+      </c>
+      <c r="C9" s="14"/>
       <c r="D9" s="14"/>
-      <c r="E9" s="19" t="s">
-        <v>27</v>
-      </c>
+      <c r="E9" s="14"/>
       <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="23" t="s">
-        <v>27</v>
-      </c>
+      <c r="G9" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="15"/>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1510,17 +1493,17 @@
       <c r="A10" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="22" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
       <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
+      <c r="F10" s="19" t="s">
+        <v>25</v>
+      </c>
       <c r="G10" s="14"/>
-      <c r="H10" s="23" t="s">
-        <v>27</v>
-      </c>
+      <c r="H10" s="15"/>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
@@ -1562,15 +1545,15 @@
         <v>30</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
-      <c r="E11" s="19" t="s">
-        <v>27</v>
-      </c>
+      <c r="E11" s="14"/>
       <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
+      <c r="G11" s="19" t="s">
+        <v>25</v>
+      </c>
       <c r="H11" s="15"/>
       <c r="I11"/>
       <c r="J11"/>
@@ -1610,18 +1593,20 @@
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
+      <c r="C12" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>25</v>
+      </c>
       <c r="E12" s="14"/>
       <c r="F12" s="14"/>
-      <c r="G12" s="19" t="s">
-        <v>27</v>
-      </c>
+      <c r="G12" s="14"/>
       <c r="H12" s="15"/>
       <c r="I12"/>
       <c r="J12"/>
@@ -1661,18 +1646,18 @@
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>27</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="C13" s="14"/>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
+      <c r="G13" s="19" t="s">
+        <v>25</v>
+      </c>
       <c r="H13" s="15"/>
       <c r="I13"/>
       <c r="J13"/>
@@ -1712,18 +1697,18 @@
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>37</v>
+        <v>48</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
-      <c r="F14" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="G14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="19" t="s">
+        <v>25</v>
+      </c>
       <c r="H14" s="15"/>
       <c r="I14"/>
       <c r="J14"/>
@@ -1763,17 +1748,17 @@
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
       <c r="F15" s="14"/>
       <c r="G15" s="19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H15" s="15"/>
       <c r="I15"/>
@@ -1813,21 +1798,13 @@
       <c r="AQ15"/>
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>27</v>
-      </c>
+      <c r="A16" s="9"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
       <c r="E16" s="14"/>
       <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
+      <c r="G16" s="19"/>
       <c r="H16" s="15"/>
       <c r="I16"/>
       <c r="J16"/>
@@ -1865,21 +1842,17 @@
       <c r="AP16"/>
       <c r="AQ16"/>
     </row>
-    <row r="17" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="H17" s="15"/>
+    <row r="17" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+      <c r="A17" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="34"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -1917,10 +1890,18 @@
       <c r="AQ17"/>
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="9"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
+      <c r="A18" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>25</v>
+      </c>
       <c r="E18" s="14"/>
       <c r="F18" s="14"/>
       <c r="G18" s="14"/>
@@ -1961,17 +1942,23 @@
       <c r="AP18"/>
       <c r="AQ18"/>
     </row>
-    <row r="19" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A19" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" s="34"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="35"/>
+    <row r="19" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="15"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -2010,16 +1997,16 @@
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>27</v>
+        <v>25</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>25</v>
       </c>
       <c r="E20" s="14"/>
       <c r="F20" s="14"/>
@@ -2063,20 +2050,22 @@
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>27</v>
+        <v>25</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>25</v>
       </c>
       <c r="E21" s="14"/>
       <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
+      <c r="G21" s="23" t="s">
+        <v>25</v>
+      </c>
       <c r="H21" s="15"/>
       <c r="I21"/>
       <c r="J21"/>
@@ -2115,18 +2104,10 @@
       <c r="AQ21"/>
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>27</v>
-      </c>
+      <c r="A22" s="9"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="14"/>
       <c r="G22" s="14"/>
@@ -2168,23 +2149,13 @@
       <c r="AQ22"/>
     </row>
     <row r="23" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>27</v>
-      </c>
+      <c r="A23" s="9"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
       <c r="E23" s="14"/>
       <c r="F23" s="14"/>
-      <c r="G23" s="24" t="s">
-        <v>27</v>
-      </c>
+      <c r="G23" s="14"/>
       <c r="H23" s="15"/>
       <c r="I23"/>
       <c r="J23"/>
@@ -2222,15 +2193,17 @@
       <c r="AP23"/>
       <c r="AQ23"/>
     </row>
-    <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="9"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="15"/>
+    <row r="24" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+      <c r="A24" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="33"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="34"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -2268,14 +2241,24 @@
       <c r="AQ24"/>
     </row>
     <row r="25" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="9"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="14"/>
+      <c r="A25" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>25</v>
+      </c>
       <c r="D25" s="14"/>
       <c r="E25" s="14"/>
       <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="15"/>
+      <c r="G25" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="H25" s="25" t="s">
+        <v>25</v>
+      </c>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
@@ -2312,17 +2295,25 @@
       <c r="AP25"/>
       <c r="AQ25"/>
     </row>
-    <row r="26" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A26" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="B26" s="34"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="34"/>
-      <c r="H26" s="35"/>
+    <row r="26" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="H26" s="15"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2361,22 +2352,24 @@
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="D27" s="14"/>
+        <v>45</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" s="24" t="s">
+        <v>25</v>
+      </c>
       <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="H27" s="26" t="s">
-        <v>27</v>
+      <c r="F27" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" s="14"/>
+      <c r="H27" s="25" t="s">
+        <v>25</v>
       </c>
       <c r="I27"/>
       <c r="J27"/>
@@ -2416,21 +2409,19 @@
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="D28" s="25" t="s">
-        <v>27</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" s="14"/>
       <c r="E28" s="14"/>
       <c r="F28" s="14"/>
       <c r="G28" s="24" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H28" s="15"/>
       <c r="I28"/>
@@ -2470,26 +2461,14 @@
       <c r="AQ28"/>
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="D29" s="25" t="s">
-        <v>27</v>
-      </c>
+      <c r="A29" s="9"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
       <c r="E29" s="14"/>
-      <c r="F29" s="25" t="s">
-        <v>27</v>
-      </c>
+      <c r="F29" s="14"/>
       <c r="G29" s="14"/>
-      <c r="H29" s="26" t="s">
-        <v>27</v>
-      </c>
+      <c r="H29" s="15"/>
       <c r="I29"/>
       <c r="J29"/>
       <c r="K29"/>
@@ -2527,21 +2506,13 @@
       <c r="AQ29"/>
     </row>
     <row r="30" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" s="25" t="s">
-        <v>27</v>
-      </c>
+      <c r="A30" s="9"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="14"/>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
       <c r="F30" s="14"/>
-      <c r="G30" s="25" t="s">
-        <v>27</v>
-      </c>
+      <c r="G30" s="14"/>
       <c r="H30" s="15"/>
       <c r="I30"/>
       <c r="J30"/>
@@ -2579,15 +2550,15 @@
       <c r="AP30"/>
       <c r="AQ30"/>
     </row>
-    <row r="31" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="9"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="15"/>
+    <row r="31" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="10"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="17"/>
       <c r="I31"/>
       <c r="J31"/>
       <c r="K31"/>
@@ -2624,15 +2595,15 @@
       <c r="AP31"/>
       <c r="AQ31"/>
     </row>
-    <row r="32" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="9"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="15"/>
+    <row r="32" spans="1:43" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A32" s="5"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
       <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
@@ -2669,110 +2640,22 @@
       <c r="AP32"/>
       <c r="AQ32"/>
     </row>
-    <row r="33" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="10"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="17"/>
-      <c r="I33"/>
-      <c r="J33"/>
-      <c r="K33"/>
-      <c r="L33"/>
-      <c r="M33"/>
-      <c r="N33"/>
-      <c r="O33"/>
-      <c r="P33"/>
-      <c r="Q33"/>
-      <c r="R33"/>
-      <c r="S33"/>
-      <c r="T33"/>
-      <c r="U33"/>
-      <c r="V33"/>
-      <c r="W33"/>
-      <c r="X33"/>
-      <c r="Y33"/>
-      <c r="Z33"/>
-      <c r="AA33"/>
-      <c r="AB33"/>
-      <c r="AC33"/>
-      <c r="AD33"/>
-      <c r="AE33"/>
-      <c r="AF33"/>
-      <c r="AG33"/>
-      <c r="AH33"/>
-      <c r="AI33"/>
-      <c r="AJ33"/>
-      <c r="AK33"/>
-      <c r="AL33"/>
-      <c r="AM33"/>
-      <c r="AN33"/>
-      <c r="AO33"/>
-      <c r="AP33"/>
-      <c r="AQ33"/>
-    </row>
-    <row r="34" spans="1:43" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A34" s="5"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34"/>
-      <c r="J34"/>
-      <c r="K34"/>
-      <c r="L34"/>
-      <c r="M34"/>
-      <c r="N34"/>
-      <c r="O34"/>
-      <c r="P34"/>
-      <c r="Q34"/>
-      <c r="R34"/>
-      <c r="S34"/>
-      <c r="T34"/>
-      <c r="U34"/>
-      <c r="V34"/>
-      <c r="W34"/>
-      <c r="X34"/>
-      <c r="Y34"/>
-      <c r="Z34"/>
-      <c r="AA34"/>
-      <c r="AB34"/>
-      <c r="AC34"/>
-      <c r="AD34"/>
-      <c r="AE34"/>
-      <c r="AF34"/>
-      <c r="AG34"/>
-      <c r="AH34"/>
-      <c r="AI34"/>
-      <c r="AJ34"/>
-      <c r="AK34"/>
-      <c r="AL34"/>
-      <c r="AM34"/>
-      <c r="AN34"/>
-      <c r="AO34"/>
-      <c r="AP34"/>
-      <c r="AQ34"/>
-    </row>
-    <row r="35" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="36" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="37" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="39" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="40" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="41" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="42" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="43" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="44" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="45" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="46" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="47" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="48" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="33" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="34" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="37" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="38" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="39" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="40" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="41" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="42" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="45" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="46" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="47" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="48" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="49" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="50" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="51" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -2803,8 +2686,6 @@
     <row r="76" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="77" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="78" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="79" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="80" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="G1:H1"/>
@@ -2815,8 +2696,8 @@
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A24:H24"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
   </mergeCells>
